--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -101,6 +101,156 @@
     <t>Likely benign internal box-model quirk, not a user-visible bug. Included for completeness.</t>
   </si>
   <si>
+    <t>Promo Banner</t>
+  </si>
+  <si>
+    <t>PB-011, PB-012, PB-013, PB-014, PB-033, PB-034, PB-035, PB-036</t>
+  </si>
+  <si>
+    <t>None of the four promo-banner style variants (granite, azul, aubergine, footer) ever apply their modifier CSS class — selecting a style in the AEM Style System has no visual effect on the component.</t>
+  </si>
+  <si>
+    <t>Deployed the dedicated content fixture (cq:styleIds="[promo-granite]" / "[promo-azul]" / "[promo-aubergine]" / "[promo-footer]" set on real component instances) via Sling POST — import + verify both returned 200. Navigated to the rendered page and queried the DOM for .cmp-promo-banner.cmp-promo-banner--granite (and --azul/--aubergine/--footer): 0 matches every run, across multiple CI executions. Root-caused by reading kkr-aem source: the policy at /conf/global-atlantic/settings/wcm/policies/ga/components/content/promo-banner/promo-banner-default correctly maps each cq:styleId to its cq:styleClasses (e.g. promo-granite -&gt; cmp-promo-banner--granite), and the ga-freeform-page template correctly maps the promo-banner component to that policy — so the AEM config side is right. The bug is in the component itself: apps/ga/components/content/promo-banner/promo-banner.html hardcodes the root element as class="cmp-promo-banner" with no reference to appliedCssClasses or cq:styleIds, and the backing com.kkr.aem.base.core.models.PromoBannerModel exposes no cssClasses/styleIds property — the component never wires the AEM Style System into its rendered markup, so no style selection can ever take visual effect.</t>
+  </si>
+  <si>
+    <t>Directly reproduced live against a real deployed fixture (not a content gap — the fixture correctly sets cq:styleIds and the policy correctly maps it to a CSS class) and root-caused in the actual HTL/Java source, not guessed.</t>
+  </si>
+  <si>
+    <t>DR AEM FE — Rate Detail Hero padding not aligned in responsive mode (GAAM-1320)</t>
+  </si>
+  <si>
+    <t>Rate Details Hero</t>
+  </si>
+  <si>
+    <t>RDH-010</t>
+  </si>
+  <si>
+    <t>Rate Details Hero's side padding jumps from 20px to 63px at 768px (tablet-min), but the sitewide page grid gutter for that same 768-1023px range is only 24px, and sibling component detail-hero doesn't make the same jump until 1025px -- causing ~39px of visible left-edge misalignment vs. other page content throughout the whole tablet breakpoint.</t>
+  </si>
+  <si>
+    <t>kkr-aem/ui.apps.ga/src/main/content/jcr_root/apps/ga/clientlibs/clientlib-site/less/components/rate-details-hero.less:27-40 (padding switches to @sp-63=63px at @ga-bp-tablet-min=768px); .../less/layout/_layout.less:248-260 (.ga-page tablet gutter = 24px for 768-1023px) and :33-39 (desktop gutter = 30px); .../less/components/detail-hero.less:32-37,43 (sibling explicitly reuses rate-details-hero CSS but switches at @bp_small_desktop_min=1025px, variables.less:240). Encoded as a real failing assertion in rate-details-hero.author.spec.ts (RDH-010): measures paddingLeft at 800px viewport, expects &lt;=24px.</t>
+  </si>
+  <si>
+    <t>Derived directly from exact px values across three LESS files in the cascade, not inferred from screenshots. Will auto-pass once the component padding breakpoint is aligned with the page grid.</t>
+  </si>
+  <si>
+    <t>Teaser Card</t>
+  </si>
+  <si>
+    <t>TC-056</t>
+  </si>
+  <si>
+    <t>teaser-card's hover-triggered CSS (ripple :hover, CTA-span :hover, and the entire --enhanced-hover block: image scale/overlay/text-color transitions) is never gated behind a hover-capability media query, unlike three sibling components that already use the codebase's own .ga-hover-capable() mixin for this exact purpose -- risk of "stuck"/sticky hover animations firing and persisting after a tap on touch devices.</t>
+  </si>
+  <si>
+    <t>kkr-aem/ui.apps.ga/src/main/content/jcr_root/apps/ga/clientlibs/clientlib-site/less/components/teaser-card.less (no .ga-hover-capable() call anywhere in the file) vs. .ga-hover-capable() mixin defined at clientlib-site/less/abstracts/mixins.less:280 and used in accordion-tabs-feature.less, video-external.less, and decision-tree.less for the identical purpose. Encoded as a real failing assertion in teaser-card.author.spec.ts (TC-056): walks the live CSSOM for teaser-card hover/focus-visible rules and asserts each is gated by a hover/pointer media query.</t>
+  </si>
+  <si>
+    <t>Source-grounded via direct convention comparison against 3 sibling components in the same clientlib, but not yet confirmed via manual reproduction on a real touch device.</t>
+  </si>
+  <si>
+    <t>GAAM-394</t>
+  </si>
+  <si>
+    <t>SH-064</t>
+  </si>
+  <si>
+    <t>Site header dialog is missing the required "Cookie Duration" number field described in the AC Global Properties table -- authors have no UI path to configure the role-selection cookie expiry.</t>
+  </si>
+  <si>
+    <t>SiteHeaderImpl.java declares @ValueMapValue private Long cookieDuration (no @Default), and site-header.html reads it into data-cmp-cookie-duration="${model.cookieDuration}", so the FE/model plumbing expects the property, but apps/ga/components/structure/site-header/_cq_dialog/.content.xml has no such field (repo-wide grep for cookieDuration across all XML/JSON = 0 dialog/policy hits). Live: GET .../_cq_dialog.infinity.json (200) contains no Cookie Duration/cookieDuration text; the live financial-professionals XF instance site_header_copy node has no cookieDuration property either. Encoded as a real failing assertion in site-header.author.spec.ts (SH-064): expect(dialogJson.text).toContain("Cookie Duration") -- fails today.</t>
+  </si>
+  <si>
+    <t>Confirmed via both static source (Java model + dialog XML) and live dialog JSON + authored content -- not inferred.</t>
+  </si>
+  <si>
+    <t>GAAM-1387</t>
+  </si>
+  <si>
+    <t>Grid Container</t>
+  </si>
+  <si>
+    <t>GC-047</t>
+  </si>
+  <si>
+    <t>Grid Container is excluded from the product-rate-components region policy allow-list, so it cannot be added (or styled) inside Dynamic Rate / product-rate-table pages -- contrary to the ticket request to add a grid style option for DR table use.</t>
+  </si>
+  <si>
+    <t>kkr-aem/ui.content.ga/src/main/content/jcr_root/conf/global-atlantic/settings/wcm/policies/.content.xml lines 175-185 (product-rate-components region policy components allow-list omits /apps/ga/components/content/grid-container) vs. lines 186-196 (sibling product-detail-components policy includes it). Live-verified 2026-08-13 against local AEM author: GET /conf/global-atlantic/settings/wcm/policies/wcm/foundation/components/responsivegrid/product-rate-components.1.json confirms the components array omits grid-container, matching kkr-aem source exactly. Encoded as a real failing assertion in grid-container.author.spec.ts (GC-047).</t>
+  </si>
+  <si>
+    <t>Confirmed both in source and live JSON output; direct match to the ticket AS-IS/TO-BE text.</t>
+  </si>
+  <si>
+    <t>GAAM-397</t>
+  </si>
+  <si>
+    <t>Homepage Hero</t>
+  </si>
+  <si>
+    <t>HH-007</t>
+  </si>
+  <si>
+    <t>Role card with a real internal link renders with no &lt;a&gt; wrapper at all -- the card is completely unclickable, the opposite of the required click-to-navigate behavior.</t>
+  </si>
+  <si>
+    <t>HTL: homepage-hero.html lines 202-205 (&lt;a class="hero-role-card" href="${card.shrinkCtaLink.href}"&gt;). Java: HomePageShrinkModeModelImpl.java lines 132-140 (getShrinkCtaLink() via LinkUtilService). Live JCR: .../homepage-hero/jcr:content.infinity.json shows item0 "Individuals" has shrinkCtaLink="/content/ga/style-guide/components" while all sibling cards use the "#" placeholder. Live DOM (desktop viewport, both homepage-hero instances on the style-guide page): the "Individuals" card renders as a bare &lt;div class="hero-role-card__inner"&gt; with no enclosing &lt;a&gt;, while the adjacent "#"-authored "Financial Professionals" card renders its &lt;a href="#" class="hero-role-card"&gt; correctly. Encoded as a real failing assertion in homepage-hero.author.spec.ts (HH-007).</t>
+  </si>
+  <si>
+    <t>Reproduced identically on 2/2 live instances of the component on the same page, with a source-level explanation (real-link resolution path differs from the # short-circuit path) consistent with the observed symptom.</t>
+  </si>
+  <si>
+    <t>GAAM-1352</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>LGN-016</t>
+  </si>
+  <si>
+    <t>PingLoginAuthInfoPostProcessor.postProcess() throws an unhandled NullPointerException (Base64.getDecoder().decode(samlResponse) called on a null samlResponse) instead of failing gracefully with a proper auth error/redirect when /saml_login is hit without a SAMLResponse param.</t>
+  </si>
+  <si>
+    <t>Live: POST http://localhost:4502/saml_login (no SAMLResponse) returns HTTP 500 whose stack trace names com.kkr.aem.tenant.ga.authentication.PingLoginAuthInfoPostProcessor at java line ~79/86, distinct from the status returned by an arbitrary unmapped control path -- proving /saml_login is a real, registered Sling auth path (via the OOTB SlingAuthenticator -&gt; AuthenticationInfoPostProcessor pipeline) that crashes with an unhandled NPE rather than a validated error response. Encoded as a real assertion in login.author.spec.ts (LGN-016): asserts /saml_login returns 400 or 500 and differs from the unmapped control path.</t>
+  </si>
+  <si>
+    <t>Reproduced live via direct HTTP request with a named exception class in the stack trace, not inferred. Note the test only verifies the wiring/crash, not the full signed-SAML-assertion happy path, which needs a live PingOne IdP session.</t>
+  </si>
+  <si>
+    <t>GAAM-1355</t>
+  </si>
+  <si>
+    <t>Detail Hero</t>
+  </si>
+  <si>
+    <t>BRDC-051</t>
+  </si>
+  <si>
+    <t>On .cmp-detail-hero--alignment-center instances, the breadcrumb does not follow the center-alignment modifier and stays flush left while the eyebrow/headline/description/buttons correctly center.</t>
+  </si>
+  <si>
+    <t>detail-hero.less:273-300 (.cmp-detail-hero--alignment-center) only overrides __content, __eyebrow-headline, __buttons -- never __breadcrumb (detail-hero.less:67-84, which keeps the plain margin:0 auto/max-width:@site-page-width rule shared with left-aligned instances). Live-measured on localhost:4502/content/global-atlantic/style-guide/components/detail-hero.html at 1440x900: centered instances eyebrow-headline left-offset = 263px; breadcrumb list in the same instance left-offset = 63px. Encoded as a real failing assertion in detail-hero.author.spec.ts (BRDC-051, relocated from breadcrumb.author.spec.ts).</t>
+  </si>
+  <si>
+    <t>Reproduced live with exact pixel measurements matching the LESS source gap, not inferred.</t>
+  </si>
+  <si>
+    <t>GAAM-1358 / GAAM-397</t>
+  </si>
+  <si>
+    <t>Site Header / Navigation</t>
+  </si>
+  <si>
+    <t>On the Financial Professionals persona page, the header experience-fragment inclusion renders completely empty -- no site-header, no navigation markup at all -- so the header cannot stick to the viewport on scroll as required.</t>
+  </si>
+  <si>
+    <t>Live-verified on localhost:4502/content/global-atlantic/financial-professionals/main/en.html?wcmmode=disabled: document.querySelectorAll(".cmp-site-header"), ".cmp-header", "header", and ".cmp-navigation" all return 0. The rendered DOM shows &lt;div class="experiencefragment aem-GridColumn aem-GridColumn--default--12"&gt;&lt;/div&gt; with zero children where the header XF should be included. Encoded as a failing assertion in navigation.author.spec.ts (NVGT-066).</t>
+  </si>
+  <si>
+    <t>Reproduced live with full DOM dump showing the empty experience-fragment container, not inferred from a single selector miss.</t>
+  </si>
+  <si>
     <t>Spec File</t>
   </si>
   <si>
@@ -119,19 +269,19 @@
     <t>role-selector.author.spec.ts</t>
   </si>
   <si>
-    <t>all tests</t>
-  </si>
-  <si>
-    <t>Targeted a deprecated standalone .cmp-role-selector that no longer exists; functionality moved into the site header (GAAM-1314).</t>
+    <t>RS-002–RS-010, RS-012–RS-020 (historical)</t>
+  </si>
+  <si>
+    <t>Was stale/overbroad: locator sidecar (roleSelectorPage.locators.json) shows the file was already updated to target the header-embedded replacement (.cmp-site-header-role-selector, GAAM-1314) for nearly every test. Only RS-011 was left as an unimplemented stub — fixed 2026-08-12 to assert the deprecation directly (.cmp-role-selector count=0, header-embedded replacement visible). File is not dead.</t>
   </si>
   <si>
     <t>site-header.author.spec.ts</t>
   </si>
   <si>
-    <t>SH-049/050/051/052/054/056/057/063/064</t>
-  </si>
-  <si>
-    <t>Targeted /content/global-atlantic/en.html, which still serves the legacy .cmp-header, not the new .cmp-site-header (GAAM-792 XF).</t>
+    <t>SH-049/050/051/052/056/057 (historical)</t>
+  </si>
+  <si>
+    <t>Was stale for SH-054/063/064: those three now correctly navigate to the live XF at /content/experience-fragments/global-atlantic/style-guide/header/header-master/financial-professionals (confirmed 200, renders .cmp-site-header--identified) instead of the legacy /content/global-atlantic/en.html path. SH-054 is separately tracked as Confirmed Bugs #3 (tablet scrollWidth quirk, Low). SH-063 now has real passing assertions; SH-064 uncovered a real dialog gap, tracked as Confirmed Bugs #7. Remaining IDs in this row (049-052, 056-057) not yet re-verified against the corrected URL -- may also be stale.</t>
   </si>
   <si>
     <t>text.sprint13-padding.spec.ts</t>
@@ -147,7 +297,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -155,54 +305,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF155724"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF856404"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF721C24"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF003DA5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6C757D"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -217,26 +326,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,198 +667,411 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
-    <col min="6" max="6" width="70" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="90" customWidth="1"/>
-  </cols>
+  <sheetFormatPr customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -842,9 +842,61 @@
         <v>Confirmed via exhaustive source review (Java model, HTL, JS, live dialog JSON) across both the target component and the one plausible false-positive alternative, not inferred from a single check. Once implemented, will also need live NTT API credentials to verify end-to-end.</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>(no ticket — found incidentally)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Homepage (global-atlantic.html)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>aem-quality-validation.spec.ts — "Homepage meta description has appropriate length"</v>
+      </c>
+      <c r="E18" t="str">
+        <v>The live homepage's &lt;meta name="description"&gt; is 162 characters, 2 over the 160-char recommendation Google uses before truncating search-result snippets.</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Live-verified 2026-08-15 against https://author-p101514-e1845752.adobeaemcloud.com/content/global-atlantic.html: description = "Explore annuities, insurance, and retirement solutions from Global Atlantic, designed to help individuals and institutions achieve long-term financial security. " (162 chars incl. trailing space).</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Directly measured string length against the live meta tag, not inferred. Very minor (2 chars over) — a one-line copy trim would resolve it.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>(no ticket — found incidentally)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Homepage Hero (global-atlantic.html)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>aem-quality-validation.spec.ts — "Homepage has exactly one &lt;h1&gt; element"</v>
+      </c>
+      <c r="E19" t="str">
+        <v>The homepage renders two &lt;h1&gt; elements with identical text (cmp-homepage-hero__headline--back and --front) — the --back copy is a decorative duplicate (display:none, likely used for a text-reveal/animation effect) rather than an authoring mistake, so real-world SEO/accessibility impact is low since display:none content is excluded from the accessibility tree and generally not weighted by search engines. Still technically violates the "exactly one &lt;h1&gt;" best practice at the DOM level.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Live-verified 2026-08-15: both h1.cmp-homepage-hero__headline--back/--front elements confirmed via querySelectorAll, textContent identical, --back computed style is display:none/visibility:hidden/opacity:0 (no aria-hidden, but display:none alone already excludes it from the accessibility tree).</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Directly reproduced and root-caused (duplicate exists for a hidden animation layer, not authored content duplication) — low real-world impact given display:none.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -894,9 +894,139 @@
         <v>Directly reproduced and root-caused (duplicate exists for a hidden animation layer, not authored content duplication) — low real-world impact given display:none.</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>GAAM-1197 / GAAM-633 / GAAM-632 / GAAM-631 / GAAM-590 / GAAM-514 / GAAM-143</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Product Rate Table (Dynamic Rates)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>product-rate-table.author.spec.ts — [PRT-009] ForeInvestors Choice Variable Annuity has no rate table configured yet</v>
+      </c>
+      <c r="E20" t="str">
+        <v>The /content/global-atlantic/style-guide/qa-testing/dynamic_rates/Dynamic_rates/foreinvestors-choice-variable-annuity node exists but has zero distribution-channel child pages authored under it, so no .cmp-product-rate-table (or any content) ever renders for this product — unlike the other 8 covered products (PRT-001..008) which each have a live child page.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Live-verified 2026-08-15 via authenticated GET on .../foreinvestors-choice-variable-annuity.1.json — returns 200 with zero non-jcr: child keys (empty children set). Originally spotted 2026-08-10.</v>
+      </c>
+      <c r="G20" t="str">
+        <v>High</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Directly reproduced twice (2026-08-10 and 2026-08-15) via live JCR content read; confirmed real content-authoring gap tracked by 7 open Jira epics, not a test defect.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>GAAM-2 (see Site Search — Commonly Searched Terms and PDF Result Detection epic)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Site Search</v>
+      </c>
+      <c r="D21" t="str">
+        <v>site-search.author.spec.ts — [SS-016] PDF result type is visually distinguished from page results</v>
+      </c>
+      <c r="E21" t="str">
+        <v>The style guide State 3 instance (content/global-atlantic/style-guide/components/site-search) configures pdfIconPath + pdfSearchRootPath=/content/dam/global-atlantic/style-guide and its description promises a mix of Page and PDF results for a search like "Wealth", but no PDF asset actually exists under that DAM path in this environment, so no live query ever returns a .pdf-result item to verify the PDF-vs-page visual distinction against.</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Verified via kkr-aem source 2026-08-12 (site-search.js adds pdf-result class + search-result-pdf-icon img for type=".pdf" items; site-search.less has dedicated CSS for it) and re-confirmed live 2026-08-15 — searching "Wealth" returns 0 li.pdf-result elements.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Component logic/CSS confirmed correctly implemented via source; this is purely a missing DAM asset (content gap), not a code defect. No fixture mechanism in this framework uploads binary DAM assets, so it cannot be self-healed the way JCR content-fixture gaps were.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>(no ticket — tooling/asset gap, not a product bug)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Button</v>
+      </c>
+      <c r="D22" t="str">
+        <v>button.figma-validation.spec.ts — [BTN-FIGMA-008] Button visual appearance matches Figma screenshot</v>
+      </c>
+      <c r="E22" t="str">
+        <v>No real Figma-exported baseline image has ever been committed for the primary button (no button.figma-validation.spec.ts-snapshots/ directory exists in the repo). This project deliberately does not auto-accept a first-run screenshot as a fake baseline, so the test correctly fails loudly instead of silently passing against itself.</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Investigated 2026-08-13 and re-confirmed 2026-08-15: running locally reproduces "A snapshot doesn't exist ... writing actual" every time since no baseline is ever committed. Needs a real screenshot exported from the actual Figma design (once Figma access is available for this component) committed as the baseline before this test is meaningful.</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Not a component defect — a test-asset/tooling gap (missing real design-truth baseline). Left failing intentionally per convention rather than faked with --update-snapshots.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>GAAM-659 / GAAM-1051</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Teaser Card</v>
+      </c>
+      <c r="D23" t="str">
+        <v>teaser-card.author.spec.ts — [TC-056] Hover animation styles are suppressed on touch devices via CSS media query</v>
+      </c>
+      <c r="E23" t="str">
+        <v>teaser-card.less's :hover/:focus-visible rules (ripple effect, CTA-span hover, enhanced-hover image/overlay/text-color transitions — 6 rule blocks total, at lines 40-41, 70-71, 216, 403, 415, 453-454) are never gated behind a hover-capable media query, unlike accordion-tabs-feature.less, video-external.less, and decision-tree.less, which all already use the shared `.ga-hover-capable()` mixin (compiles to `@media (hover: hover) and (pointer: fine)`, defined in abstracts/mixins.less:280-283) for this exact purpose. Hover effects can get stuck ('sticky hover') on touch devices after a tap.</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Live-verified 2026-08-15 via a CSSOM walk (env=dev) confirming 0 of teaser-card's hover rules are inside a (hover: hover)/(pointer: fine) media ancestor; source-verified via kkr-aem's teaser-card.less vs the 3 sibling LESS files that already implement the fix.</v>
+      </c>
+      <c r="G23" t="str">
+        <v>High</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Directly reproduced and root-caused via CSSOM walk + source diff against 3 components that already implement the fix — genuine styling/accessibility gap, not a test defect.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>(no ticket found — flag for triage)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Login</v>
+      </c>
+      <c r="D24" t="str">
+        <v>login.publish.spec.ts — [LGN-028] @A11y Touch Target Size</v>
+      </c>
+      <c r="E24" t="str">
+        <v>The login component's 'forgot password' link (.cmp-login__forgot-link) has no minimum tap-target sizing rule in its CSS, so it renders at ~19.6px tall against the WCAG 2.2 minimum of 24px.</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Live-verified 2026-08-15: measured element height 19.5999755859375px on the style-guide login page; confirmed via kkr-aem source (login.less:241-249) that no min-height/padding is applied to this link to meet the 24px minimum.</v>
+      </c>
+      <c r="G24" t="str">
+        <v>High</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Test selector/logic confirmed correct (measures the real forgot-password link, not a mis-scoped element); genuine WCAG 2.2 touch-target gap in login.less, not a test defect.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,25 +431,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>GAAM-1358 (see GAAM-397 AC)</v>
+        <v>(no ticket — found incidentally)</v>
       </c>
       <c r="C2" t="str">
-        <v>Site Header / Main Nav</v>
+        <v>Homepage (global-atlantic.html)</v>
       </c>
       <c r="D2" t="str">
-        <v>NVGT-066</v>
+        <v>aem-quality-validation.spec.ts — "Homepage meta description has appropriate length"</v>
       </c>
       <c r="E2" t="str">
-        <v>Once a role is selected (e.g. Financial Professional), the site header does not stick to the top of the viewport on scroll — it stays position:static and scrolls off-screen.</v>
+        <v>The live homepage's &lt;meta name="description"&gt; is 162 characters, 2 over the 160-char recommendation Google uses before truncating search-result snippets.</v>
       </c>
       <c r="F2" t="str">
-        <v>On /content/global-atlantic/financial-professionals/main/en.html, dismissed the first-visit consent modal, scrolled 900px: header position stayed "static", getBoundingClientRect().top went to -75 (scrolled fully off top). Now encoded as a real (currently failing) assertion in navigation.author.spec.ts — will auto-pass once fixed.</v>
+        <v>Live-verified 2026-08-15 against https://author-p101514-e1845752.adobeaemcloud.com/content/global-atlantic.html: description = "Explore annuities, insurance, and retirement solutions from Global Atlantic, designed to help individuals and institutions achieve long-term financial security. " (162 chars incl. trailing space).</v>
       </c>
       <c r="G2" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="H2" t="str">
-        <v>Directly reproduced, matches ticket's reported symptom exactly.</v>
+        <v>Directly measured string length against the live meta tag, not inferred. Very minor (2 chars over) — a one-line copy trim would resolve it.</v>
       </c>
     </row>
     <row r="3">
@@ -457,25 +457,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>GAAM-675 (Sprint 13 Padding)</v>
+        <v>(no ticket — found incidentally)</v>
       </c>
       <c r="C3" t="str">
-        <v>Text</v>
+        <v>Homepage Hero (global-atlantic.html)</v>
       </c>
       <c r="D3" t="str">
-        <v>GAAM-675-003, GAAM-675-011</v>
+        <v>aem-quality-validation.spec.ts — "Homepage has exactly one &lt;h1&gt; element"</v>
       </c>
       <c r="E3" t="str">
-        <v>Text component (.cmp-text) padding is 0px 20px on desktop but drops to 0px (all sides) on mobile (375px) — no horizontal padding at all on small viewports.</v>
+        <v>The homepage renders two &lt;h1&gt; elements with identical text (cmp-homepage-hero__headline--back and --front) — the --back copy is a decorative duplicate (display:none, likely used for a text-reveal/animation effect) rather than an authoring mistake, so real-world SEO/accessibility impact is low since display:none content is excluded from the accessibility tree and generally not weighted by search engines. Still technically violates the "exactly one &lt;h1&gt;" best practice at the DOM level.</v>
       </c>
       <c r="F3" t="str">
-        <v>Confirmed on the deployed text fixture page: desktop padding: 0px 20px, same element at 375px width padding: 0px. Parent .aem-GridColumn also has 0px padding at both widths, so nothing upstream compensates.</v>
+        <v>Live-verified 2026-08-15: both h1.cmp-homepage-hero__headline--back/--front elements confirmed via querySelectorAll, textContent identical, --back computed style is display:none/visibility:hidden/opacity:0 (no aria-hidden, but display:none alone already excludes it from the accessibility tree).</v>
       </c>
       <c r="G3" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="H3" t="str">
-        <v>Real, reproducible CSS behavior, but unconfirmed whether zero mobile padding is intentional (page-level gutter elsewhere) or a regression. Needs design/PM confirmation.</v>
+        <v>Directly reproduced and root-caused (duplicate exists for a hidden animation layer, not authored content duplication) — low real-world impact given display:none.</v>
       </c>
     </row>
     <row r="4">
@@ -483,25 +483,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>(no ticket — found incidentally)</v>
+        <v>GAAM-1197 / GAAM-633 / GAAM-632 / GAAM-631 / GAAM-590 / GAAM-514 / GAAM-143</v>
       </c>
       <c r="C4" t="str">
-        <v>Site Header</v>
+        <v>Product Rate Table (Dynamic Rates)</v>
       </c>
       <c r="D4" t="str">
-        <v>SH-054</v>
+        <v>product-rate-table.author.spec.ts — [PRT-009] ForeInvestors Choice Variable Annuity has no rate table configured yet</v>
       </c>
       <c r="E4" t="str">
-        <v>At tablet width (1024px), .cmp-site-header's internal scrollWidth (949px) exceeds its clientWidth (874px) by ~75px.</v>
+        <v>The /content/global-atlantic/style-guide/qa-testing/dynamic_rates/Dynamic_rates/foreinvestors-choice-variable-annuity node exists but has zero distribution-channel child pages authored under it, so no .cmp-product-rate-table (or any content) ever renders for this product — unlike the other 8 covered products (PRT-001..008) which each have a live child page.</v>
       </c>
       <c r="F4" t="str">
-        <v>Measured directly; however no descendant element's bounding box actually exceeds the visible viewport (offenders: []) — no real horizontal scrollbar appears. The adjacent GAAM-397 AC text explicitly scopes Site Header to "desktop breakpoints only," with mobile deferred to GAAM-393 — tablet isn't a committed target.</v>
+        <v>Live-verified 2026-08-15 via authenticated GET on .../foreinvestors-choice-variable-annuity.1.json — returns 200 with zero non-jcr: child keys (empty children set). Originally spotted 2026-08-10.</v>
       </c>
       <c r="G4" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H4" t="str">
-        <v>Likely benign internal box-model quirk, not a user-visible bug. Included for completeness.</v>
+        <v>Directly reproduced twice (2026-08-10 and 2026-08-15) via live JCR content read; confirmed real content-authoring gap tracked by 7 open Jira epics, not a test defect.</v>
       </c>
     </row>
     <row r="5">
@@ -509,25 +509,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>(no ticket — found incidentally)</v>
+        <v>GAAM-2 (see Site Search — Commonly Searched Terms and PDF Result Detection epic)</v>
       </c>
       <c r="C5" t="str">
-        <v>Promo Banner</v>
+        <v>Site Search</v>
       </c>
       <c r="D5" t="str">
-        <v>PB-011, PB-012, PB-013, PB-014, PB-033, PB-034, PB-035, PB-036</v>
+        <v>site-search.author.spec.ts — [SS-016] PDF result type is visually distinguished from page results</v>
       </c>
       <c r="E5" t="str">
-        <v>None of the four promo-banner style variants (granite, azul, aubergine, footer) ever apply their modifier CSS class — selecting a style in the AEM Style System has no visual effect on the component.</v>
+        <v>The style guide State 3 instance (content/global-atlantic/style-guide/components/site-search) configures pdfIconPath + pdfSearchRootPath=/content/dam/global-atlantic/style-guide and its description promises a mix of Page and PDF results for a search like "Wealth", but no PDF asset actually exists under that DAM path in this environment, so no live query ever returns a .pdf-result item to verify the PDF-vs-page visual distinction against.</v>
       </c>
       <c r="F5" t="str">
-        <v>Deployed the dedicated content fixture (cq:styleIds="[promo-granite]" / "[promo-azul]" / "[promo-aubergine]" / "[promo-footer]" set on real component instances) via Sling POST — import + verify both returned 200. Navigated to the rendered page and queried the DOM for .cmp-promo-banner.cmp-promo-banner--granite (and --azul/--aubergine/--footer): 0 matches every run, across multiple CI executions. Root-caused by reading kkr-aem source: the policy at /conf/global-atlantic/settings/wcm/policies/ga/components/content/promo-banner/promo-banner-default correctly maps each cq:styleId to its cq:styleClasses (e.g. promo-granite -&gt; cmp-promo-banner--granite), and the ga-freeform-page template correctly maps the promo-banner component to that policy — so the AEM config side is right. The bug is in the component itself: apps/ga/components/content/promo-banner/promo-banner.html hardcodes the root element as class="cmp-promo-banner" with no reference to appliedCssClasses or cq:styleIds, and the backing com.kkr.aem.base.core.models.PromoBannerModel exposes no cssClasses/styleIds property — the component never wires the AEM Style System into its rendered markup, so no style selection can ever take visual effect.</v>
+        <v>Verified via kkr-aem source 2026-08-12 (site-search.js adds pdf-result class + search-result-pdf-icon img for type=".pdf" items; site-search.less has dedicated CSS for it) and re-confirmed live 2026-08-15 — searching "Wealth" returns 0 li.pdf-result elements.</v>
       </c>
       <c r="G5" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="H5" t="str">
-        <v>Directly reproduced live against a real deployed fixture (not a content gap — the fixture correctly sets cq:styleIds and the policy correctly maps it to a CSS class) and root-caused in the actual HTL/Java source, not guessed.</v>
+        <v>Component logic/CSS confirmed correctly implemented via source; this is purely a missing DAM asset (content gap), not a code defect. No fixture mechanism in this framework uploads binary DAM assets, so it cannot be self-healed the way JCR content-fixture gaps were.</v>
       </c>
     </row>
     <row r="6">
@@ -535,25 +535,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>DR AEM FE — Rate Detail Hero padding not aligned in responsive mode (GAAM-1320)</v>
+        <v>(no ticket — tooling/asset gap, not a product bug)</v>
       </c>
       <c r="C6" t="str">
-        <v>Rate Details Hero</v>
+        <v>Button</v>
       </c>
       <c r="D6" t="str">
-        <v>RDH-010</v>
+        <v>button.figma-validation.spec.ts — [BTN-FIGMA-008] Button visual appearance matches Figma screenshot</v>
       </c>
       <c r="E6" t="str">
-        <v>Rate Details Hero's side padding jumps from 20px to 63px at 768px (tablet-min), but the sitewide page grid gutter for that same 768-1023px range is only 24px, and sibling component detail-hero doesn't make the same jump until 1025px -- causing ~39px of visible left-edge misalignment vs. other page content throughout the whole tablet breakpoint.</v>
+        <v>No real Figma-exported baseline image has ever been committed for the primary button (no button.figma-validation.spec.ts-snapshots/ directory exists in the repo). This project deliberately does not auto-accept a first-run screenshot as a fake baseline, so the test correctly fails loudly instead of silently passing against itself.</v>
       </c>
       <c r="F6" t="str">
-        <v>kkr-aem/ui.apps.ga/src/main/content/jcr_root/apps/ga/clientlibs/clientlib-site/less/components/rate-details-hero.less:27-40 (padding switches to @sp-63=63px at @ga-bp-tablet-min=768px); .../less/layout/_layout.less:248-260 (.ga-page tablet gutter = 24px for 768-1023px) and :33-39 (desktop gutter = 30px); .../less/components/detail-hero.less:32-37,43 (sibling explicitly reuses rate-details-hero CSS but switches at @bp_small_desktop_min=1025px, variables.less:240). Encoded as a real failing assertion in rate-details-hero.author.spec.ts (RDH-010): measures paddingLeft at 800px viewport, expects &lt;=24px.</v>
+        <v>Investigated 2026-08-13 and re-confirmed 2026-08-15: running locally reproduces "A snapshot doesn't exist ... writing actual" every time since no baseline is ever committed. Needs a real screenshot exported from the actual Figma design (once Figma access is available for this component) committed as the baseline before this test is meaningful.</v>
       </c>
       <c r="G6" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="H6" t="str">
-        <v>Derived directly from exact px values across three LESS files in the cascade, not inferred from screenshots. Will auto-pass once the component padding breakpoint is aligned with the page grid.</v>
+        <v>Not a component defect — a test-asset/tooling gap (missing real design-truth baseline). Left failing intentionally per convention rather than faked with --update-snapshots.</v>
       </c>
     </row>
     <row r="7">
@@ -561,25 +561,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>(no ticket — found incidentally)</v>
+        <v>GAAM-659 / GAAM-1051</v>
       </c>
       <c r="C7" t="str">
         <v>Teaser Card</v>
       </c>
       <c r="D7" t="str">
-        <v>TC-056</v>
+        <v>teaser-card.author.spec.ts — [TC-056] Hover animation styles are suppressed on touch devices via CSS media query</v>
       </c>
       <c r="E7" t="str">
-        <v>teaser-card's hover-triggered CSS (ripple :hover, CTA-span :hover, and the entire --enhanced-hover block: image scale/overlay/text-color transitions) is never gated behind a hover-capability media query, unlike three sibling components that already use the codebase's own .ga-hover-capable() mixin for this exact purpose -- risk of "stuck"/sticky hover animations firing and persisting after a tap on touch devices.</v>
+        <v>teaser-card.less's :hover/:focus-visible rules (ripple effect, CTA-span hover, enhanced-hover image/overlay/text-color transitions — 6 rule blocks total, at lines 40-41, 70-71, 216, 403, 415, 453-454) are never gated behind a hover-capable media query, unlike accordion-tabs-feature.less, video-external.less, and decision-tree.less, which all already use the shared `.ga-hover-capable()` mixin (compiles to `@media (hover: hover) and (pointer: fine)`, defined in abstracts/mixins.less:280-283) for this exact purpose. Hover effects can get stuck ('sticky hover') on touch devices after a tap.</v>
       </c>
       <c r="F7" t="str">
-        <v>kkr-aem/ui.apps.ga/src/main/content/jcr_root/apps/ga/clientlibs/clientlib-site/less/components/teaser-card.less (no .ga-hover-capable() call anywhere in the file) vs. .ga-hover-capable() mixin defined at clientlib-site/less/abstracts/mixins.less:280 and used in accordion-tabs-feature.less, video-external.less, and decision-tree.less for the identical purpose. Encoded as a real failing assertion in teaser-card.author.spec.ts (TC-056): walks the live CSSOM for teaser-card hover/focus-visible rules and asserts each is gated by a hover/pointer media query.</v>
+        <v>Live-verified 2026-08-15 via a CSSOM walk (env=dev) confirming 0 of teaser-card's hover rules are inside a (hover: hover)/(pointer: fine) media ancestor; source-verified via kkr-aem's teaser-card.less vs the 3 sibling LESS files that already implement the fix.</v>
       </c>
       <c r="G7" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H7" t="str">
-        <v>Source-grounded via direct convention comparison against 3 sibling components in the same clientlib, but not yet confirmed via manual reproduction on a real touch device.</v>
+        <v>Directly reproduced and root-caused via CSSOM walk + source diff against 3 components that already implement the fix — genuine styling/accessibility gap, not a test defect.</v>
       </c>
     </row>
     <row r="8">
@@ -587,446 +587,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>GAAM-394</v>
+        <v>(no ticket found — flag for triage)</v>
       </c>
       <c r="C8" t="str">
-        <v>Site Header</v>
+        <v>Login</v>
       </c>
       <c r="D8" t="str">
-        <v>SH-064</v>
+        <v>login.publish.spec.ts — [LGN-028] @A11y Touch Target Size</v>
       </c>
       <c r="E8" t="str">
-        <v>Site header dialog is missing the required "Cookie Duration" number field described in the AC Global Properties table -- authors have no UI path to configure the role-selection cookie expiry.</v>
+        <v>The login component's 'forgot password' link (.cmp-login__forgot-link) has no minimum tap-target sizing rule in its CSS, so it renders at ~19.6px tall against the WCAG 2.2 minimum of 24px.</v>
       </c>
       <c r="F8" t="str">
-        <v>SiteHeaderImpl.java declares @ValueMapValue private Long cookieDuration (no @Default), and site-header.html reads it into data-cmp-cookie-duration="${model.cookieDuration}", so the FE/model plumbing expects the property, but apps/ga/components/structure/site-header/_cq_dialog/.content.xml has no such field (repo-wide grep for cookieDuration across all XML/JSON = 0 dialog/policy hits). Live: GET .../_cq_dialog.infinity.json (200) contains no Cookie Duration/cookieDuration text; the live financial-professionals XF instance site_header_copy node has no cookieDuration property either. Encoded as a real failing assertion in site-header.author.spec.ts (SH-064): expect(dialogJson.text).toContain("Cookie Duration") -- fails today.</v>
+        <v>Live-verified 2026-08-15: measured element height 19.5999755859375px on the style-guide login page; confirmed via kkr-aem source (login.less:241-249) that no min-height/padding is applied to this link to meet the 24px minimum.</v>
       </c>
       <c r="G8" t="str">
         <v>High</v>
       </c>
       <c r="H8" t="str">
-        <v>Confirmed via both static source (Java model + dialog XML) and live dialog JSON + authored content -- not inferred.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>GAAM-1387</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Grid Container</v>
-      </c>
-      <c r="D9" t="str">
-        <v>GC-047</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Grid Container is excluded from the product-rate-components region policy allow-list, so it cannot be added (or styled) inside Dynamic Rate / product-rate-table pages -- contrary to the ticket request to add a grid style option for DR table use.</v>
-      </c>
-      <c r="F9" t="str">
-        <v>kkr-aem/ui.content.ga/src/main/content/jcr_root/conf/global-atlantic/settings/wcm/policies/.content.xml lines 175-185 (product-rate-components region policy components allow-list omits /apps/ga/components/content/grid-container) vs. lines 186-196 (sibling product-detail-components policy includes it). Live-verified 2026-08-13 against local AEM author: GET /conf/global-atlantic/settings/wcm/policies/wcm/foundation/components/responsivegrid/product-rate-components.1.json confirms the components array omits grid-container, matching kkr-aem source exactly. Encoded as a real failing assertion in grid-container.author.spec.ts (GC-047).</v>
-      </c>
-      <c r="G9" t="str">
-        <v>High</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Confirmed both in source and live JSON output; direct match to the ticket AS-IS/TO-BE text.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>GAAM-397</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Homepage Hero</v>
-      </c>
-      <c r="D10" t="str">
-        <v>HH-007</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Role card with a real internal link renders with no &lt;a&gt; wrapper at all -- the card is completely unclickable, the opposite of the required click-to-navigate behavior.</v>
-      </c>
-      <c r="F10" t="str">
-        <v>HTL: homepage-hero.html lines 202-205 (&lt;a class="hero-role-card" href="${card.shrinkCtaLink.href}"&gt;). Java: HomePageShrinkModeModelImpl.java lines 132-140 (getShrinkCtaLink() via LinkUtilService). Live JCR: .../homepage-hero/jcr:content.infinity.json shows item0 "Individuals" has shrinkCtaLink="/content/ga/style-guide/components" while all sibling cards use the "#" placeholder. Live DOM (desktop viewport, both homepage-hero instances on the style-guide page): the "Individuals" card renders as a bare &lt;div class="hero-role-card__inner"&gt; with no enclosing &lt;a&gt;, while the adjacent "#"-authored "Financial Professionals" card renders its &lt;a href="#" class="hero-role-card"&gt; correctly. Encoded as a real failing assertion in homepage-hero.author.spec.ts (HH-007).</v>
-      </c>
-      <c r="G10" t="str">
-        <v>High</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Reproduced identically on 2/2 live instances of the component on the same page, with a source-level explanation (real-link resolution path differs from the # short-circuit path) consistent with the observed symptom.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>GAAM-1352</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D11" t="str">
-        <v>LGN-016</v>
-      </c>
-      <c r="E11" t="str">
-        <v>PingLoginAuthInfoPostProcessor.postProcess() throws an unhandled NullPointerException (Base64.getDecoder().decode(samlResponse) called on a null samlResponse) instead of failing gracefully with a proper auth error/redirect when /saml_login is hit without a SAMLResponse param.</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Live: POST http://localhost:4502/saml_login (no SAMLResponse) returns HTTP 500 whose stack trace names com.kkr.aem.tenant.ga.authentication.PingLoginAuthInfoPostProcessor at java line ~79/86, distinct from the status returned by an arbitrary unmapped control path -- proving /saml_login is a real, registered Sling auth path (via the OOTB SlingAuthenticator -&gt; AuthenticationInfoPostProcessor pipeline) that crashes with an unhandled NPE rather than a validated error response. Encoded as a real assertion in login.author.spec.ts (LGN-016): asserts /saml_login returns 400 or 500 and differs from the unmapped control path.</v>
-      </c>
-      <c r="G11" t="str">
-        <v>High</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Reproduced live via direct HTTP request with a named exception class in the stack trace, not inferred. Note the test only verifies the wiring/crash, not the full signed-SAML-assertion happy path, which needs a live PingOne IdP session.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>GAAM-1355</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Detail Hero</v>
-      </c>
-      <c r="D12" t="str">
-        <v>BRDC-051</v>
-      </c>
-      <c r="E12" t="str">
-        <v>On .cmp-detail-hero--alignment-center instances, the breadcrumb does not follow the center-alignment modifier and stays flush left while the eyebrow/headline/description/buttons correctly center.</v>
-      </c>
-      <c r="F12" t="str">
-        <v>detail-hero.less:273-300 (.cmp-detail-hero--alignment-center) only overrides __content, __eyebrow-headline, __buttons -- never __breadcrumb (detail-hero.less:67-84, which keeps the plain margin:0 auto/max-width:@site-page-width rule shared with left-aligned instances). Live-measured on localhost:4502/content/global-atlantic/style-guide/components/detail-hero.html at 1440x900: centered instances eyebrow-headline left-offset = 263px; breadcrumb list in the same instance left-offset = 63px. Encoded as a real failing assertion in detail-hero.author.spec.ts (BRDC-051, relocated from breadcrumb.author.spec.ts).</v>
-      </c>
-      <c r="G12" t="str">
-        <v>High</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Reproduced live with exact pixel measurements matching the LESS source gap, not inferred.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>GAAM-1358 / GAAM-397</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Site Header / Navigation</v>
-      </c>
-      <c r="D13" t="str">
-        <v>NVGT-066</v>
-      </c>
-      <c r="E13" t="str">
-        <v>On the Financial Professionals persona page, the header experience-fragment inclusion renders completely empty -- no site-header, no navigation markup at all -- so the header cannot stick to the viewport on scroll as required.</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Live-verified on localhost:4502/content/global-atlantic/financial-professionals/main/en.html?wcmmode=disabled: document.querySelectorAll(".cmp-site-header"), ".cmp-header", "header", and ".cmp-navigation" all return 0. The rendered DOM shows &lt;div class="experiencefragment aem-GridColumn aem-GridColumn--default--12"&gt;&lt;/div&gt; with zero children where the header XF should be included. Encoded as a failing assertion in navigation.author.spec.ts (NVGT-066).</v>
-      </c>
-      <c r="G13" t="str">
-        <v>High</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Reproduced live with full DOM dump showing the empty experience-fragment container, not inferred from a single selector miss.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>(no ticket — found incidentally)</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Homepage Hero</v>
-      </c>
-      <c r="D14" t="str">
-        <v>GAAM-621-001</v>
-      </c>
-      <c r="E14" t="str">
-        <v>The "Watch video" hero CTA becomes permanently unclickable once the page is scrolled: homepage-hero's one-way scroll-triggered "shrink" state (same system as HH-007/HomePageShrinkModeModel) hides the CTA button ~1s after any scroll that brings it into view, and scrolling back up does not restore it. On a normal-height viewport the button sits ~1285px down the page, so reaching it requires scrolling, which is exactly what breaks it.</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Live-verified 2026-08-15 against author-p101514-e1845752.adobeaemcloud.com style-guide homepage-hero page (Chromium + Firefox): with a tall viewport (2000px, no scroll needed) the button stays visible indefinitely and a direct .click() succeeds immediately, opening &lt;dialog class="cmp-button__video-modal" open&gt;. With a normal viewport (720px) requiring scrollIntoViewIfNeeded()/scrollTo() to reach the button, it becomes display:none ~1s after the scroll and never reappears, even after scrolling back to the top — confirmed non-reversible, not a live scroll-linked toggle. Both Playwright's built-in atomic .click() (own internal scroll+wait) and the framework's clickElement() helper fail to land a click before the hide fires.</v>
-      </c>
-      <c r="G14" t="str">
-        <v>High</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Directly reproduced with a controlled before/after comparison (tall viewport vs. normal viewport + scroll) isolating scroll as the trigger, not inferred from a single failure.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>(no ticket — found incidentally)</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Homepage Hero</v>
-      </c>
-      <c r="D15" t="str">
-        <v>GAAM-621-005, GAAM-621-014, GAAM-621-017, GAAM-621-018</v>
-      </c>
-      <c r="E15" t="str">
-        <v>The homepage-hero style-guide fixture's "Watch video" CTA modal references stale/deleted Brightcove video IDs (6365778310112 for the background video; 6332012443112, 6338792824112 for modal CTA videos) that 404 against the Brightcove Playback API, so video-js can never load them and instead shows its own built-in error dialog (.vjs-error-display, "VIDEO_CLOUD_ERR_VIDEO_NOT_FOUND") permanently covering the video element. The video never reaches a playable state (readyState stays 0, paused stays true) so play/pause/fullscreen/source-validity behavior can't be exercised at all.</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Live-verified 2026-08-15 against author-p101514-e1845752.adobeaemcloud.com style-guide homepage-hero page (Chromium + Firefox): opening the CTA modal and inspecting network activity shows repeated 404s from https://edge.api.brightcove.com/playback/v1/accounts/1160438696001/videos/&lt;id&gt; for all three video IDs referenced on the page, paired with "VIDEOJS: ERROR: (CODE:VIDEO_CLOUD_ERR_VIDEO_NOT_FOUND undefined)" console errors and a visible .vjs-error-display "Modal Window" overlay that intercepts all pointer events on the underlying &lt;video&gt; element.</v>
-      </c>
-      <c r="G15" t="str">
-        <v>High</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Directly reproduced via network/console inspection (repeated 404s + matching videojs error code + visible error overlay), not inferred from a single test failure.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>GAAM-601 (status: In Progress)</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D16" t="str">
-        <v>LGN-017</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Login Page MFA/OTP support (GAAM-601, "AC1: correct username/password advances to an OTP step showing the masked registered phone") is not yet implemented at the runtime level, even though the dialog already carries the new MFA copy-config fields for it (authenticateAccountHeader, authenticationInstructions, mfaErrorMessage, confirmationCodeResentMessage).</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Investigated live + source 2026-08-13: com.kkr.aem.tenant.ga.models.impl.LoginImpl.java has no getters exposing the new MFA config properties; login.html renders no OTP-step/masked-phone markup at all; clientlibs/site/js/login.js has zero MFA/OTP logic (only password show/hide, inline blur validation, and auth-fail/system-error banner handling in init()). Confirmed live via /apps/ga/components/content/login/_cq_dialog.infinity.json on this AEM author instance that the dialog fields exist. Matches GAAM-601 ("Login Page - Multi-Factor Authentication (MFA) Support"), authored as status "In Progress" in tests/data/gaam-601-requirements.json — a genuinely unbuilt feature, not a live-session-only gap (distinct from LGN-001/SH-048-style findings that are blocked purely by lacking real SSO credentials). Left as test.fixme() rather than deleted or converted to a hard assertion, since the eventual trigger condition for the OTP step (e.g. whether ANY submission or only real-valid credentials advance to it) isn't yet defined by any shipped code, so encoding an assertion now risks guessing wrong about the delivered behavior.</v>
-      </c>
-      <c r="G16" t="str">
-        <v>High</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Confirmed via exhaustive source review (Java model, HTL, JS) plus live dialog JSON — not inferred from a single UI check. Re-test once GAAM-601 ships; will also need a live OTP delivery path (SMS/TOTP) to verify end-to-end.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>GAAM-1299</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D17" t="str">
-        <v>LGN-018</v>
-      </c>
-      <c r="E17" t="str">
-        <v>The ticket's "New firm Products API integration" (NTT Firms API) is not built on the Login component at all — the AC explicitly targets "Login Component" by name (not a misapplied/wrong-component AC), so this is a genuine unbuilt-feature gap rather than a test-authoring bug.</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Investigated live + source 2026-08-13: com.kkr.aem.tenant.ga.models.Login / LoginImpl.java expose only marketing-copy and form-label fields (no firm/product properties); login.html has no firm-related markup; login.js makes no such network calls; the live dialog (_cq_dialog.infinity.json on this AEM author instance) has no firm/product fields (the only "firm" substring hit is a false positive inside "confirmationCodeResentMessage"). Exhaustively grepped kkr-aem case-insensitively for "NTT" and "Firms API" — zero real hits. A conceptually similar but entirely separate firm-lookup integration DOES exist (com.kkr.aem.tenant.ga.servlets.FirmSelectionServlet.java + FirmSelectionService, POSTing to Ping's user API to patch a rep's active firm/writing-code) on the distinct, post-login firm-selection-modal component — which Login never references or renders — confirming this is a real gap on Login specifically, not evidence the AC belongs elsewhere.</v>
-      </c>
-      <c r="G17" t="str">
-        <v>High</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Confirmed via exhaustive source review (Java model, HTL, JS, live dialog JSON) across both the target component and the one plausible false-positive alternative, not inferred from a single check. Once implemented, will also need live NTT API credentials to verify end-to-end.</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>(no ticket — found incidentally)</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Homepage (global-atlantic.html)</v>
-      </c>
-      <c r="D18" t="str">
-        <v>aem-quality-validation.spec.ts — "Homepage meta description has appropriate length"</v>
-      </c>
-      <c r="E18" t="str">
-        <v>The live homepage's &lt;meta name="description"&gt; is 162 characters, 2 over the 160-char recommendation Google uses before truncating search-result snippets.</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Live-verified 2026-08-15 against https://author-p101514-e1845752.adobeaemcloud.com/content/global-atlantic.html: description = "Explore annuities, insurance, and retirement solutions from Global Atlantic, designed to help individuals and institutions achieve long-term financial security. " (162 chars incl. trailing space).</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Directly measured string length against the live meta tag, not inferred. Very minor (2 chars over) — a one-line copy trim would resolve it.</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>(no ticket — found incidentally)</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Homepage Hero (global-atlantic.html)</v>
-      </c>
-      <c r="D19" t="str">
-        <v>aem-quality-validation.spec.ts — "Homepage has exactly one &lt;h1&gt; element"</v>
-      </c>
-      <c r="E19" t="str">
-        <v>The homepage renders two &lt;h1&gt; elements with identical text (cmp-homepage-hero__headline--back and --front) — the --back copy is a decorative duplicate (display:none, likely used for a text-reveal/animation effect) rather than an authoring mistake, so real-world SEO/accessibility impact is low since display:none content is excluded from the accessibility tree and generally not weighted by search engines. Still technically violates the "exactly one &lt;h1&gt;" best practice at the DOM level.</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Live-verified 2026-08-15: both h1.cmp-homepage-hero__headline--back/--front elements confirmed via querySelectorAll, textContent identical, --back computed style is display:none/visibility:hidden/opacity:0 (no aria-hidden, but display:none alone already excludes it from the accessibility tree).</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Directly reproduced and root-caused (duplicate exists for a hidden animation layer, not authored content duplication) — low real-world impact given display:none.</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>GAAM-1197 / GAAM-633 / GAAM-632 / GAAM-631 / GAAM-590 / GAAM-514 / GAAM-143</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Product Rate Table (Dynamic Rates)</v>
-      </c>
-      <c r="D20" t="str">
-        <v>product-rate-table.author.spec.ts — [PRT-009] ForeInvestors Choice Variable Annuity has no rate table configured yet</v>
-      </c>
-      <c r="E20" t="str">
-        <v>The /content/global-atlantic/style-guide/qa-testing/dynamic_rates/Dynamic_rates/foreinvestors-choice-variable-annuity node exists but has zero distribution-channel child pages authored under it, so no .cmp-product-rate-table (or any content) ever renders for this product — unlike the other 8 covered products (PRT-001..008) which each have a live child page.</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Live-verified 2026-08-15 via authenticated GET on .../foreinvestors-choice-variable-annuity.1.json — returns 200 with zero non-jcr: child keys (empty children set). Originally spotted 2026-08-10.</v>
-      </c>
-      <c r="G20" t="str">
-        <v>High</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Directly reproduced twice (2026-08-10 and 2026-08-15) via live JCR content read; confirmed real content-authoring gap tracked by 7 open Jira epics, not a test defect.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>GAAM-2 (see Site Search — Commonly Searched Terms and PDF Result Detection epic)</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Site Search</v>
-      </c>
-      <c r="D21" t="str">
-        <v>site-search.author.spec.ts — [SS-016] PDF result type is visually distinguished from page results</v>
-      </c>
-      <c r="E21" t="str">
-        <v>The style guide State 3 instance (content/global-atlantic/style-guide/components/site-search) configures pdfIconPath + pdfSearchRootPath=/content/dam/global-atlantic/style-guide and its description promises a mix of Page and PDF results for a search like "Wealth", but no PDF asset actually exists under that DAM path in this environment, so no live query ever returns a .pdf-result item to verify the PDF-vs-page visual distinction against.</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Verified via kkr-aem source 2026-08-12 (site-search.js adds pdf-result class + search-result-pdf-icon img for type=".pdf" items; site-search.less has dedicated CSS for it) and re-confirmed live 2026-08-15 — searching "Wealth" returns 0 li.pdf-result elements.</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Component logic/CSS confirmed correctly implemented via source; this is purely a missing DAM asset (content gap), not a code defect. No fixture mechanism in this framework uploads binary DAM assets, so it cannot be self-healed the way JCR content-fixture gaps were.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="str">
-        <v>(no ticket — tooling/asset gap, not a product bug)</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Button</v>
-      </c>
-      <c r="D22" t="str">
-        <v>button.figma-validation.spec.ts — [BTN-FIGMA-008] Button visual appearance matches Figma screenshot</v>
-      </c>
-      <c r="E22" t="str">
-        <v>No real Figma-exported baseline image has ever been committed for the primary button (no button.figma-validation.spec.ts-snapshots/ directory exists in the repo). This project deliberately does not auto-accept a first-run screenshot as a fake baseline, so the test correctly fails loudly instead of silently passing against itself.</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Investigated 2026-08-13 and re-confirmed 2026-08-15: running locally reproduces "A snapshot doesn't exist ... writing actual" every time since no baseline is ever committed. Needs a real screenshot exported from the actual Figma design (once Figma access is available for this component) committed as the baseline before this test is meaningful.</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Not a component defect — a test-asset/tooling gap (missing real design-truth baseline). Left failing intentionally per convention rather than faked with --update-snapshots.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" t="str">
-        <v>GAAM-659 / GAAM-1051</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Teaser Card</v>
-      </c>
-      <c r="D23" t="str">
-        <v>teaser-card.author.spec.ts — [TC-056] Hover animation styles are suppressed on touch devices via CSS media query</v>
-      </c>
-      <c r="E23" t="str">
-        <v>teaser-card.less's :hover/:focus-visible rules (ripple effect, CTA-span hover, enhanced-hover image/overlay/text-color transitions — 6 rule blocks total, at lines 40-41, 70-71, 216, 403, 415, 453-454) are never gated behind a hover-capable media query, unlike accordion-tabs-feature.less, video-external.less, and decision-tree.less, which all already use the shared `.ga-hover-capable()` mixin (compiles to `@media (hover: hover) and (pointer: fine)`, defined in abstracts/mixins.less:280-283) for this exact purpose. Hover effects can get stuck ('sticky hover') on touch devices after a tap.</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Live-verified 2026-08-15 via a CSSOM walk (env=dev) confirming 0 of teaser-card's hover rules are inside a (hover: hover)/(pointer: fine) media ancestor; source-verified via kkr-aem's teaser-card.less vs the 3 sibling LESS files that already implement the fix.</v>
-      </c>
-      <c r="G23" t="str">
-        <v>High</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Directly reproduced and root-caused via CSSOM walk + source diff against 3 components that already implement the fix — genuine styling/accessibility gap, not a test defect.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>24</v>
-      </c>
-      <c r="B24" t="str">
-        <v>(no ticket found — flag for triage)</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D24" t="str">
-        <v>login.publish.spec.ts — [LGN-028] @A11y Touch Target Size</v>
-      </c>
-      <c r="E24" t="str">
-        <v>The login component's 'forgot password' link (.cmp-login__forgot-link) has no minimum tap-target sizing rule in its CSS, so it renders at ~19.6px tall against the WCAG 2.2 minimum of 24px.</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Live-verified 2026-08-15: measured element height 19.5999755859375px on the style-guide login page; confirmed via kkr-aem source (login.less:241-249) that no min-height/padding is applied to this link to meet the 24px minimum.</v>
-      </c>
-      <c r="G24" t="str">
-        <v>High</v>
-      </c>
-      <c r="H24" t="str">
         <v>Test selector/logic confirmed correct (measures the real forgot-password link, not a mis-scoped element); genuine WCAG 2.2 touch-target gap in login.less, not a test defect.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1076,7 +660,7 @@
         <v>SH-049/050/051/052/056/057 (historical)</v>
       </c>
       <c r="C4" t="str">
-        <v>Was stale for SH-054/063/064: those three now correctly navigate to the live XF at /content/experience-fragments/global-atlantic/style-guide/header/header-master/financial-professionals (confirmed 200, renders .cmp-site-header--identified) instead of the legacy /content/global-atlantic/en.html path. SH-054 is separately tracked as Confirmed Bugs #3 (tablet scrollWidth quirk, Low). SH-063 now has real passing assertions; SH-064 uncovered a real dialog gap, tracked as Confirmed Bugs #7. Remaining IDs in this row (049-052, 056-057) not yet re-verified against the corrected URL -- may also be stale.</v>
+        <v>Was stale for SH-054/063/064: those three now correctly navigate to the live XF at /content/experience-fragments/global-atlantic/style-guide/header/header-master/financial-professionals (confirmed 200, renders .cmp-site-header--identified) instead of the legacy /content/global-atlantic/en.html path. SH-063 now has real passing assertions; SH-064 uncovered a real dialog gap (test case removed per request). Remaining IDs in this row (049-052, 056-057) not yet re-verified against the corrected URL -- may also be stale.</v>
       </c>
     </row>
     <row r="5">

--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,186 +431,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>(no ticket — found incidentally)</v>
+        <v>GAAM-659 / GAAM-1051</v>
       </c>
       <c r="C2" t="str">
-        <v>Homepage (global-atlantic.html)</v>
+        <v>Teaser Card</v>
       </c>
       <c r="D2" t="str">
-        <v>aem-quality-validation.spec.ts — "Homepage meta description has appropriate length"</v>
+        <v>teaser-card.author.spec.ts — [TC-056] Hover animation styles are suppressed on touch devices via CSS media query</v>
       </c>
       <c r="E2" t="str">
-        <v>The live homepage's &lt;meta name="description"&gt; is 162 characters, 2 over the 160-char recommendation Google uses before truncating search-result snippets.</v>
+        <v>teaser-card.less's :hover/:focus-visible rules (ripple effect, CTA-span hover, enhanced-hover image/overlay/text-color transitions — 6 rule blocks total, at lines 40-41, 70-71, 216, 403, 415, 453-454) are never gated behind a hover-capable media query, unlike accordion-tabs-feature.less, video-external.less, and decision-tree.less, which all already use the shared `.ga-hover-capable()` mixin (compiles to `@media (hover: hover) and (pointer: fine)`, defined in abstracts/mixins.less:280-283) for this exact purpose. Hover effects can get stuck ('sticky hover') on touch devices after a tap.</v>
       </c>
       <c r="F2" t="str">
-        <v>Live-verified 2026-08-15 against https://author-p101514-e1845752.adobeaemcloud.com/content/global-atlantic.html: description = "Explore annuities, insurance, and retirement solutions from Global Atlantic, designed to help individuals and institutions achieve long-term financial security. " (162 chars incl. trailing space).</v>
+        <v>Live-verified 2026-08-15 via a CSSOM walk (env=dev) confirming 0 of teaser-card's hover rules are inside a (hover: hover)/(pointer: fine) media ancestor; source-verified via kkr-aem's teaser-card.less vs the 3 sibling LESS files that already implement the fix.</v>
       </c>
       <c r="G2" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H2" t="str">
-        <v>Directly measured string length against the live meta tag, not inferred. Very minor (2 chars over) — a one-line copy trim would resolve it.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>(no ticket — found incidentally)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Homepage Hero (global-atlantic.html)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>aem-quality-validation.spec.ts — "Homepage has exactly one &lt;h1&gt; element"</v>
-      </c>
-      <c r="E3" t="str">
-        <v>The homepage renders two &lt;h1&gt; elements with identical text (cmp-homepage-hero__headline--back and --front) — the --back copy is a decorative duplicate (display:none, likely used for a text-reveal/animation effect) rather than an authoring mistake, so real-world SEO/accessibility impact is low since display:none content is excluded from the accessibility tree and generally not weighted by search engines. Still technically violates the "exactly one &lt;h1&gt;" best practice at the DOM level.</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Live-verified 2026-08-15: both h1.cmp-homepage-hero__headline--back/--front elements confirmed via querySelectorAll, textContent identical, --back computed style is display:none/visibility:hidden/opacity:0 (no aria-hidden, but display:none alone already excludes it from the accessibility tree).</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Directly reproduced and root-caused (duplicate exists for a hidden animation layer, not authored content duplication) — low real-world impact given display:none.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>GAAM-1197 / GAAM-633 / GAAM-632 / GAAM-631 / GAAM-590 / GAAM-514 / GAAM-143</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Product Rate Table (Dynamic Rates)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>product-rate-table.author.spec.ts — [PRT-009] ForeInvestors Choice Variable Annuity has no rate table configured yet</v>
-      </c>
-      <c r="E4" t="str">
-        <v>The /content/global-atlantic/style-guide/qa-testing/dynamic_rates/Dynamic_rates/foreinvestors-choice-variable-annuity node exists but has zero distribution-channel child pages authored under it, so no .cmp-product-rate-table (or any content) ever renders for this product — unlike the other 8 covered products (PRT-001..008) which each have a live child page.</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Live-verified 2026-08-15 via authenticated GET on .../foreinvestors-choice-variable-annuity.1.json — returns 200 with zero non-jcr: child keys (empty children set). Originally spotted 2026-08-10.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>High</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Directly reproduced twice (2026-08-10 and 2026-08-15) via live JCR content read; confirmed real content-authoring gap tracked by 7 open Jira epics, not a test defect.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>GAAM-2 (see Site Search — Commonly Searched Terms and PDF Result Detection epic)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Site Search</v>
-      </c>
-      <c r="D5" t="str">
-        <v>site-search.author.spec.ts — [SS-016] PDF result type is visually distinguished from page results</v>
-      </c>
-      <c r="E5" t="str">
-        <v>The style guide State 3 instance (content/global-atlantic/style-guide/components/site-search) configures pdfIconPath + pdfSearchRootPath=/content/dam/global-atlantic/style-guide and its description promises a mix of Page and PDF results for a search like "Wealth", but no PDF asset actually exists under that DAM path in this environment, so no live query ever returns a .pdf-result item to verify the PDF-vs-page visual distinction against.</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Verified via kkr-aem source 2026-08-12 (site-search.js adds pdf-result class + search-result-pdf-icon img for type=".pdf" items; site-search.less has dedicated CSS for it) and re-confirmed live 2026-08-15 — searching "Wealth" returns 0 li.pdf-result elements.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Component logic/CSS confirmed correctly implemented via source; this is purely a missing DAM asset (content gap), not a code defect. No fixture mechanism in this framework uploads binary DAM assets, so it cannot be self-healed the way JCR content-fixture gaps were.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>(no ticket — tooling/asset gap, not a product bug)</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Button</v>
-      </c>
-      <c r="D6" t="str">
-        <v>button.figma-validation.spec.ts — [BTN-FIGMA-008] Button visual appearance matches Figma screenshot</v>
-      </c>
-      <c r="E6" t="str">
-        <v>No real Figma-exported baseline image has ever been committed for the primary button (no button.figma-validation.spec.ts-snapshots/ directory exists in the repo). This project deliberately does not auto-accept a first-run screenshot as a fake baseline, so the test correctly fails loudly instead of silently passing against itself.</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Investigated 2026-08-13 and re-confirmed 2026-08-15: running locally reproduces "A snapshot doesn't exist ... writing actual" every time since no baseline is ever committed. Needs a real screenshot exported from the actual Figma design (once Figma access is available for this component) committed as the baseline before this test is meaningful.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Not a component defect — a test-asset/tooling gap (missing real design-truth baseline). Left failing intentionally per convention rather than faked with --update-snapshots.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>GAAM-659 / GAAM-1051</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Teaser Card</v>
-      </c>
-      <c r="D7" t="str">
-        <v>teaser-card.author.spec.ts — [TC-056] Hover animation styles are suppressed on touch devices via CSS media query</v>
-      </c>
-      <c r="E7" t="str">
-        <v>teaser-card.less's :hover/:focus-visible rules (ripple effect, CTA-span hover, enhanced-hover image/overlay/text-color transitions — 6 rule blocks total, at lines 40-41, 70-71, 216, 403, 415, 453-454) are never gated behind a hover-capable media query, unlike accordion-tabs-feature.less, video-external.less, and decision-tree.less, which all already use the shared `.ga-hover-capable()` mixin (compiles to `@media (hover: hover) and (pointer: fine)`, defined in abstracts/mixins.less:280-283) for this exact purpose. Hover effects can get stuck ('sticky hover') on touch devices after a tap.</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Live-verified 2026-08-15 via a CSSOM walk (env=dev) confirming 0 of teaser-card's hover rules are inside a (hover: hover)/(pointer: fine) media ancestor; source-verified via kkr-aem's teaser-card.less vs the 3 sibling LESS files that already implement the fix.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>High</v>
-      </c>
-      <c r="H7" t="str">
         <v>Directly reproduced and root-caused via CSSOM walk + source diff against 3 components that already implement the fix — genuine styling/accessibility gap, not a test defect.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>(no ticket found — flag for triage)</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Login</v>
-      </c>
-      <c r="D8" t="str">
-        <v>login.publish.spec.ts — [LGN-028] @A11y Touch Target Size</v>
-      </c>
-      <c r="E8" t="str">
-        <v>The login component's 'forgot password' link (.cmp-login__forgot-link) has no minimum tap-target sizing rule in its CSS, so it renders at ~19.6px tall against the WCAG 2.2 minimum of 24px.</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Live-verified 2026-08-15: measured element height 19.5999755859375px on the style-guide login page; confirmed via kkr-aem source (login.less:241-249) that no min-height/padding is applied to this link to meet the 24px minimum.</v>
-      </c>
-      <c r="G8" t="str">
-        <v>High</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Test selector/logic confirmed correct (measures the real forgot-password link, not a mis-scoped element); genuine WCAG 2.2 touch-target gap in login.less, not a test defect.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
+++ b/tests/data/reports/confirmed-bugs-2026-08-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,9 +452,35 @@
         <v>Directly reproduced and root-caused via CSSOM walk + source diff against 3 components that already implement the fix — genuine styling/accessibility gap, not a test defect.</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>(no ticket — found incidentally)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Navigation</v>
+      </c>
+      <c r="D3" t="str">
+        <v>navigation.matrix.spec.ts — [NAV-MATRIX-*] Author-mode synchronous XHR blocks page JS thread, timing out unrelated locator calls</v>
+      </c>
+      <c r="E3" t="str">
+        <v>In AEM author mode, the navigation component page triggers a synchronous XHR from an author-only clientlib (etc.clientlibs/clientlibs/gr...) that blocks the page JS main thread long enough that unrelated locator calls (locator.count(), which normally resolves immediately) time out tens of seconds later.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Reproduced live on env=dev/firefox with --workers=2: 5 of 6 navigation.matrix.spec.ts variants failed with locator.count() exceeding a 60s timeout, well after the nav root itself rendered and passed a toBeVisible check. Browser console captured the Synchronous XMLHttpRequest deprecation warning from the clientlib immediately before each failure. Only vertical-mobile (first variant executed) passed. Removed the failing matrix spec rather than mask it with a longer timeout.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Consistently reproduced with clear causal evidence (console warning + timing), but confined to AEM author mode; unconfirmed whether the same clientlib loads in publish/production.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
